--- a/backend/data/financials_by_company/002167.SZ.xlsx
+++ b/backend/data/financials_by_company/002167.SZ.xlsx
@@ -3958,197 +3958,197 @@
       </c>
       <c r="DF1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>longName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="ES1" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>86 75 4855 01988</t>
+          <t>86 75 4855 08091</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Guangdong Orient Zirconic Ind Sci &amp; Tech Co.,Ltd, together with its subsidiaries, engages in the research, development, production, and sale of zirconium products in China and internationally. The company offers zirconium oxychloride, zirconium dioxide, fused zirconia, zirconium silicate, and compound zirconia; ceramic knife and accessories, as well as grinding media products; and zircon sand, titanium concentrate, monazite, composite zirconium oxide, and zirconium oxide ceramic structural parts. Its products are used in solid oxide fuel cells, aerospace, electronic and structural ceramics, bioceramics, color glazes, high-temperature refractory materials, nuclear and new energy, photovoltaics, new energy battery materials, artificial gems, ceramic-based brake pads, dental implants, and optical communication devices. The company also provides technology promotion services. Guangdong Orient Zirconic Ind Sci &amp; Tech Co.,Ltd was founded in 1995 and is headquartered in Shantou, China.</t>
+          <t>Guangdong Orient Zirconic Ind Sci &amp; Tech Co.,Ltd, together with its subsidiaries, engages in the research and development, production, and sale of zirconium series products in China and internationally. The company offers zirconium products, such as fused zirconia, zirconium dioxide, stabilized zirconia, zirconium silicate, and zirconium oxychloride; and ceramic products, including ceramic knife, zirconium structural ceramics, and grinding media. Its products are used in electronic ceramics, bio ceramics, structural ceramics, color glazes, high-temperature refractory materials, and nuclear energy industries, as well as photovoltaics, new energy battery materials, artificial gemstones, ceramic-based brake pads, dental implants, and optical communication devices. The company was founded in 1995 and is headquartered in Shantou, China.</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4253,28 +4253,28 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>16.13</v>
+        <v>26.05</v>
       </c>
       <c r="V2" t="n">
-        <v>16.13</v>
+        <v>21.78</v>
       </c>
       <c r="W2" t="n">
-        <v>16.13</v>
+        <v>23.73</v>
       </c>
       <c r="X2" t="n">
-        <v>16.13</v>
+        <v>26.85</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.13</v>
+        <v>26.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.13</v>
+        <v>21.78</v>
       </c>
       <c r="AA2" t="n">
-        <v>16.13</v>
+        <v>23.73</v>
       </c>
       <c r="AB2" t="n">
-        <v>16.13</v>
+        <v>26.85</v>
       </c>
       <c r="AC2" t="n">
         <v>1338854400</v>
@@ -4283,34 +4283,34 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.437</v>
+        <v>0.363</v>
       </c>
       <c r="AF2" t="n">
-        <v>253.42857</v>
+        <v>357.7143</v>
       </c>
       <c r="AG2" t="n">
-        <v>70.95999999999999</v>
+        <v>100.16</v>
       </c>
       <c r="AH2" t="n">
-        <v>5813405</v>
+        <v>166261020</v>
       </c>
       <c r="AI2" t="n">
-        <v>5813405</v>
+        <v>166261020</v>
       </c>
       <c r="AJ2" t="n">
-        <v>40667482</v>
+        <v>61898916</v>
       </c>
       <c r="AK2" t="n">
-        <v>80372054</v>
+        <v>148177763</v>
       </c>
       <c r="AL2" t="n">
-        <v>80372054</v>
+        <v>148177763</v>
       </c>
       <c r="AM2" t="n">
-        <v>16.13</v>
+        <v>25.03</v>
       </c>
       <c r="AN2" t="n">
-        <v>14.67</v>
+        <v>25.04</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -4319,31 +4319,31 @@
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13742703616</v>
+        <v>19397820416</v>
       </c>
       <c r="AR2" t="n">
-        <v>12495480329</v>
+        <v>18809067724</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.23</v>
+        <v>10.43</v>
       </c>
       <c r="AT2" t="n">
-        <v>16.6</v>
+        <v>26.85</v>
       </c>
       <c r="AU2" t="n">
-        <v>19.92</v>
+        <v>26.71</v>
       </c>
       <c r="AV2" t="n">
         <v>1.076923</v>
       </c>
       <c r="AW2" t="n">
-        <v>10.888353</v>
+        <v>15.368907</v>
       </c>
       <c r="AX2" t="n">
-        <v>13.2868</v>
+        <v>14.868</v>
       </c>
       <c r="AY2" t="n">
-        <v>13.2828</v>
+        <v>13.59875</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -4360,19 +4360,19 @@
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>13646505984</v>
+        <v>19301621760</v>
       </c>
       <c r="BE2" t="n">
         <v>0.042930003</v>
       </c>
       <c r="BF2" t="n">
-        <v>562885367</v>
+        <v>565883352</v>
       </c>
       <c r="BG2" t="n">
         <v>774673300</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.30723</v>
+        <v>0.29563</v>
       </c>
       <c r="BI2" t="n">
         <v>0.01446</v>
@@ -4384,7 +4384,7 @@
         <v>2.297</v>
       </c>
       <c r="BL2" t="n">
-        <v>7.7231174</v>
+        <v>10.901176</v>
       </c>
       <c r="BM2" t="n">
         <v>1767139200</v>
@@ -4416,16 +4416,16 @@
         <v>1435104000</v>
       </c>
       <c r="BV2" t="n">
-        <v>10.812</v>
+        <v>15.293</v>
       </c>
       <c r="BW2" t="n">
-        <v>110.471</v>
+        <v>156.25</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.67671514</v>
+        <v>1.4598677</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BZ2" t="n">
         <v>0.033333</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="CC2" t="n">
-        <v>17.74</v>
+        <v>25.04</v>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
@@ -4541,149 +4541,149 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1189647000000</v>
+      </c>
+      <c r="DH2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DG2" t="n">
-        <v>1782111876</v>
-      </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DI2" t="n">
+        <v>1783062258</v>
+      </c>
+      <c r="DJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="inlineStr">
         <is>
           <t>SHZ</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>finmb_22534323</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
         <is>
           <t>Asia/Shanghai</t>
         </is>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>CST</t>
         </is>
       </c>
-      <c r="DL2" t="n">
+      <c r="DO2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DM2" t="inlineStr">
+      <c r="DP2" t="inlineStr">
         <is>
           <t>cn_market</t>
         </is>
       </c>
-      <c r="DN2" t="b">
+      <c r="DQ2" t="b">
         <v>0</v>
       </c>
-      <c r="DO2" t="n">
-        <v>9.981405000000001</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>17.74</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>GUANGDONG ORIENT ZIRCONIC IND S</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>Guangdong Orient Zirconic Ind Sci &amp; Tech Co.,Ltd</t>
-        </is>
+      <c r="DR2" t="n">
+        <v>-3.877153</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.25</v>
+        <v>25.04</v>
       </c>
       <c r="DT2" t="n">
-        <v>4.4531994</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0.33515966</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>4.4572</v>
+        <v>-1.0099983</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>23.73 - 26.85</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
       </c>
       <c r="DW2" t="n">
-        <v>0.33556178</v>
+        <v>61898916</v>
       </c>
       <c r="DX2" t="n">
-        <v>15</v>
+        <v>14.610001</v>
       </c>
       <c r="DY2" t="n">
-        <v>15</v>
+        <v>1.4007671</v>
       </c>
       <c r="DZ2" t="inlineStr">
         <is>
-          <t>Guangdong Orient Zirconic Ind Sci &amp; Tech Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="EB2" t="b">
-        <v>0</v>
+          <t>10.43 - 26.85</t>
+        </is>
+      </c>
+      <c r="EA2" t="n">
+        <v>-1.8099995</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.06741153</v>
       </c>
       <c r="EC2" t="n">
-        <v>1618657140</v>
+        <v>145.98677</v>
       </c>
       <c r="ED2" t="n">
         <v>1618657140</v>
       </c>
       <c r="EE2" t="n">
+        <v>1618657140</v>
+      </c>
+      <c r="EF2" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="EF2" t="b">
-        <v>0</v>
-      </c>
       <c r="EG2" t="n">
-        <v>1189647000000</v>
+        <v>0.25</v>
       </c>
       <c r="EH2" t="n">
-        <v>1.6100006</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>16.13 - 16.13</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
+        <v>10.172001</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>0.684154</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>11.441251</v>
       </c>
       <c r="EK2" t="n">
-        <v>40667482</v>
+        <v>0.8413458</v>
       </c>
       <c r="EL2" t="n">
-        <v>8.51</v>
+        <v>15</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.9219935500000001</v>
+        <v>15</v>
       </c>
       <c r="EN2" t="inlineStr">
         <is>
-          <t>9.23 - 16.6</t>
-        </is>
-      </c>
-      <c r="EO2" t="n">
-        <v>1.1399994</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>0.06867466</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>67.67152</v>
+          <t>Guangdong Orient Zirconic Ind Sci &amp; Tech Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>GUANGDONG ORIENT ZIRCONIC IND S</t>
+        </is>
       </c>
       <c r="ER2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
+          <t>Guangdong Orient Zirconic Ind Sci &amp; Tech Co.,Ltd</t>
         </is>
       </c>
       <c r="ES2" t="inlineStr"/>
